--- a/コミッション報告_2026年10月/朴G/コミッション明細_2026年10月_1706_HidakaShingo.xlsx
+++ b/コミッション報告_2026年10月/朴G/コミッション明細_2026年10月_1706_HidakaShingo.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="38">
   <si>
     <r>
       <rPr>
@@ -327,7 +327,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2026.8</t>
+      <t xml:space="preserve">2026.9</t>
     </r>
     <r>
       <rPr>
@@ -392,59 +392,6 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026.9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">に</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">か月分お支払い済み（みなし年払いは年</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回のため今回は対象外）</t>
     </r>
   </si>
   <si>
@@ -1244,7 +1191,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="16" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1252,10 +1199,10 @@
         <v>3</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>28</v>
@@ -1286,7 +1233,7 @@
         <v>2100</v>
       </c>
       <c r="M13" s="17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1294,10 +1241,10 @@
         <v>4</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>28</v>
@@ -1328,7 +1275,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1336,10 +1283,10 @@
         <v>5</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>24</v>
@@ -1370,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
